--- a/data/excel/relation.xlsx
+++ b/data/excel/relation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,41 +767,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>毛泽东</t>
+          <t>中国人民解放军</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PARTICIPATED_IN</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>渡江战役</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/69112/index.html</t>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>董必武</t>
+          <t>毛泽东</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>李达</t>
+          <t>董必武</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>毛泽东</t>
+          <t>李达</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>八七会议</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>古田会议</t>
+          <t>八七会议</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>朱德</t>
+          <t>毛泽东</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>毛泽东</t>
+          <t>朱德</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>遵义会议</t>
+          <t>古田会议</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>周恩来</t>
+          <t>毛泽东</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>朱德</t>
+          <t>周恩来</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>刘少奇</t>
+          <t>朱德</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>毛泽东</t>
+          <t>刘少奇</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>遵义会议</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>周恩来</t>
+          <t>毛泽东</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>朱德</t>
+          <t>周恩来</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>刘少奇</t>
+          <t>朱德</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>邓小平</t>
+          <t>刘少奇</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>中国共产党第十一届中央委员会第三次全体会议</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>毛泽东</t>
+          <t>邓小平</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AUTHORED</t>
+          <t>PARTICIPATED_IN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>论持久战</t>
+          <t>中国共产党第十一届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1321,17 +1321,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AUTHORED</t>
+          <t>PARTICIPATED_IN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>中国社会各阶级的分析</t>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1345,7 +1345,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>毛泽东</t>
+          <t>周恩来</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AUTHORED</t>
+          <t>PARTICIPATED_IN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>实践论</t>
+          <t>论持久战</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>矛盾论</t>
+          <t>中国社会各阶级的分析</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>论联合政府</t>
+          <t>星星之火，可以燎原</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1491,24 +1491,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HELD_POSITION</t>
+          <t>AUTHORED</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>中国共产党</t>
+          <t>实践论</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Organization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>中央委员会主席</t>
-        </is>
-      </c>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
@@ -1519,7 +1515,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>陈独秀</t>
+          <t>毛泽东</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1529,24 +1525,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HELD_POSITION</t>
+          <t>AUTHORED</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>中国共产党</t>
+          <t>矛盾论</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Organization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>中央局书记</t>
-        </is>
-      </c>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
@@ -1557,7 +1549,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>朱德</t>
+          <t>毛泽东</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1567,24 +1559,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HELD_POSITION</t>
+          <t>AUTHORED</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>中国工农红军</t>
+          <t>论联合政府</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Organization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>总司令</t>
-        </is>
-      </c>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
@@ -1595,7 +1583,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>朱德</t>
+          <t>毛泽东</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1610,7 +1598,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>八路军</t>
+          <t>中国共产党</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1620,7 +1608,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>总指挥</t>
+          <t>中央委员会主席</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1633,7 +1621,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>彭德怀</t>
+          <t>陈独秀</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1648,7 +1636,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>八路军</t>
+          <t>中国共产党</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1658,7 +1646,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>副总指挥</t>
+          <t>中央局书记</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1671,7 +1659,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>陈毅</t>
+          <t>朱德</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1686,7 +1674,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>新四军</t>
+          <t>中国工农红军</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1696,7 +1684,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>代理军长</t>
+          <t>总司令</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1724,7 +1712,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>中国人民解放军</t>
+          <t>八路军</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1734,7 +1722,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>总司令</t>
+          <t>总指挥</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1747,109 +1735,121 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>彭德怀</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HELD_IN</t>
+          <t>HELD_POSITION</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>八路军</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>副总指挥</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+          <t>http://cpc.people.com.cn/GB/69112/index.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>八七会议</t>
+          <t>陈毅</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HELD_IN</t>
+          <t>HELD_POSITION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>汉口</t>
+          <t>新四军</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>代理军长</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+          <t>http://cpc.people.com.cn/GB/69112/index.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>古田会议</t>
+          <t>朱德</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HELD_IN</t>
+          <t>HELD_POSITION</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>古田</t>
+          <t>中国人民解放军</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>总司令</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+          <t>http://cpc.people.com.cn/GB/69112/index.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>遵义会议</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>遵义</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>瓦窑堡会议</t>
+          <t>八七会议</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>瓦窑堡</t>
+          <t>汉口</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>洛川会议</t>
+          <t>古田会议</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>洛川</t>
+          <t>古田</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>遵义会议</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>延安</t>
+          <t>遵义</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>中国共产党第十一届中央委员会第三次全体会议</t>
+          <t>瓦窑堡会议</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>瓦窑堡</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>中国社会主义青年团第一次全国代表大会</t>
+          <t>洛川会议</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>洛川</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2053,22 +2053,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>五四运动</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OCCURRED_IN</t>
+          <t>HELD_IN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>延安</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2080,29 +2080,29 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>南昌起义</t>
+          <t>中国共产党第十一届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OCCURRED_IN</t>
+          <t>HELD_IN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>南昌</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2114,29 +2114,29 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>井冈山会师</t>
+          <t>中国社会主义青年团第一次全国代表大会</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OCCURRED_IN</t>
+          <t>HELD_IN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>井冈山</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2148,29 +2148,29 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>西安事变</t>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OCCURRED_IN</t>
+          <t>HELD_IN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>西柏坡</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2182,24 +2182,24 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>卢沟桥事变</t>
+          <t>中国共产党第十八次全国代表大会</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OCCURRED_IN</t>
+          <t>HELD_IN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2216,24 +2216,24 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>开国大典</t>
+          <t>中国共产党第二十次全国代表大会</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OCCURRED_IN</t>
+          <t>HELD_IN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2250,150 +2250,150 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>五四运动</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PRODUCED</t>
+          <t>OCCURRED_IN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>中国共产党第一个纲领</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>南昌起义</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PRODUCED</t>
+          <t>OCCURRED_IN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>论联合政府</t>
+          <t>南昌</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>井冈山会师</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FOUNDED</t>
+          <t>OCCURRED_IN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>中国共产党</t>
+          <t>井冈山</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>中国社会主义青年团第一次全国代表大会</t>
+          <t>西安事变</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FOUNDED</t>
+          <t>OCCURRED_IN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>中国共产主义青年团</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>井冈山会师</t>
+          <t>卢沟桥事变</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FOUNDED</t>
+          <t>OCCURRED_IN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中国工农红军</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2427,35 +2427,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>中国工农红军</t>
+          <t>开国大典</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>REORGANIZED_TO</t>
+          <t>OCCURRED_IN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>八路军</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1937年8月</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
@@ -2465,74 +2461,282 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>八路军</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REORGANIZED_TO</t>
+          <t>PRODUCED</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中国人民解放军</t>
+          <t>中国共产党第一个纲领</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1946年</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>中国共产党第七次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PRODUCED</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>论联合政府</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>中国共产党第一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FOUNDED</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>中国共产党</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>中国社会主义青年团第一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FOUNDED</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>中国共产主义青年团</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>井冈山会师</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FOUNDED</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>中国工农红军</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>中国工农红军</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REORGANIZED_TO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>八路军</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1937年8月</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>八路军</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>REORGANIZED_TO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>中国人民解放军</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1946年</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>新四军</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>REORGANIZED_TO</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>中国人民解放军</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
         <is>
           <t>1946年</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>

--- a/data/excel/relation.xlsx
+++ b/data/excel/relation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2742,6 +2742,550 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>中国共产党第二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>中国共产党第三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>中国共产党第四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>中国共产党第五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>汉口</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>中国共产党第六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>莫斯科</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>中国共产党第八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>中国共产党第九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>中国共产党第十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>中国共产党第十一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>中国共产党第十二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>中国共产党第十三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>中国共产党第十四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>中国共产党第十五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>中国共产党第十六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>中国共产党第十七次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>中国共产党第十九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HELD_IN</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
